--- a/api_testdata.xlsx
+++ b/api_testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\playwrightpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C0D162-8835-47B0-8023-D380B4C48EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F35174-4624-4363-A6C1-C857ABC80454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -79,13 +79,13 @@
     <t>page=2</t>
   </si>
   <si>
-    <t>reqres_7db3d4a09a9a4c588a77dae9f4d4029b</t>
-  </si>
-  <si>
     <t>skip_keys</t>
   </si>
   <si>
     <t>id,createdAt</t>
+  </si>
+  <si>
+    <t>reqres_7ab3d4a09a9a4c588a77dae9f4d4029b</t>
   </si>
 </sst>
 </file>
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -524,7 +524,7 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">

--- a/api_testdata.xlsx
+++ b/api_testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\playwrightpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F35174-4624-4363-A6C1-C857ABC80454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F97A4D-2B48-4E77-81DE-8E1A3D0CE617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
     <t>id,createdAt</t>
   </si>
   <si>
-    <t>reqres_7ab3d4a09a9a4c588a77dae9f4d4029b</t>
+    <t>reqres_7db3d4a09b9a4c588a77dae9f4d4029b</t>
   </si>
 </sst>
 </file>
